--- a/02_Inputs/Data/Charts/Module 1 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 1 - Datasets for Charts.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29012"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Data\Charts\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5B0104-4B9A-41AD-AB22-318B428C1095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="585" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5BA57CD-7C89-46B4-8856-171F83B73066}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="6" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="9" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M1_C1_2" sheetId="1" r:id="rId1"/>
@@ -20,6 +15,9 @@
     <sheet name="M1_C1_12" sheetId="6" r:id="rId5"/>
     <sheet name="M1_C1_13" sheetId="7" r:id="rId6"/>
     <sheet name="M1_C1_14" sheetId="8" r:id="rId7"/>
+    <sheet name="M1_C3_25_1" sheetId="11" r:id="rId8"/>
+    <sheet name="M1_C3_25_2" sheetId="10" r:id="rId9"/>
+    <sheet name="(Legacy) M1_C1_12" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,9 +40,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="201">
-  <si>
-    <t>ï»¿3-letter ISO code</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="217">
+  <si>
+    <t>ISO Code</t>
   </si>
   <si>
     <t>Country</t>
@@ -596,6 +594,93 @@
     <t>Category</t>
   </si>
   <si>
+    <t xml:space="preserve">Final Energy Consumption: Total </t>
+  </si>
+  <si>
+    <t>Final Energy Consumption: Modern renewable sources</t>
+  </si>
+  <si>
+    <t>Final Energy Consumption: Traditional use of biomass</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Heat: Total</t>
+  </si>
+  <si>
+    <t>Heat: Modern renewable sources</t>
+  </si>
+  <si>
+    <t>Heat: Traditional use of biomass</t>
+  </si>
+  <si>
+    <t>Developing countries</t>
+  </si>
+  <si>
+    <t>Developed countries</t>
+  </si>
+  <si>
+    <t>Least developed countries</t>
+  </si>
+  <si>
+    <t>Landlocked developing countries</t>
+  </si>
+  <si>
+    <t>Small island developing States</t>
+  </si>
+  <si>
+    <t>PES (GtCO2/year)</t>
+  </si>
+  <si>
+    <t>COP 27 Announcement (GtCO2/year)</t>
+  </si>
+  <si>
+    <t>COP 28 Announcement (GtCO2/year)</t>
+  </si>
+  <si>
+    <t>1.5°C Scenario (GtCO2/year)</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Electricity (USD/kWh)</t>
+  </si>
+  <si>
+    <t>Caribbean</t>
+  </si>
+  <si>
+    <t>Central America</t>
+  </si>
+  <si>
+    <t>Southern Cone</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Andean Region</t>
+  </si>
+  <si>
+    <t>Gasoline (USD/litre)</t>
+  </si>
+  <si>
+    <t>Diesel (USD/litre)</t>
+  </si>
+  <si>
+    <t>Rest of the world</t>
+  </si>
+  <si>
+    <t>Caribbean Oil Importers</t>
+  </si>
+  <si>
+    <t>Caribbean Oil Exporters</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total Final Energy Consumption </t>
   </si>
   <si>
@@ -605,46 +690,7 @@
     <t>Traditional use of biomass</t>
   </si>
   <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
     <t>Heat</t>
-  </si>
-  <si>
-    <t>2015 (watts per capita)</t>
-  </si>
-  <si>
-    <t>2022 (watts per capita)</t>
-  </si>
-  <si>
-    <t>Developing countries</t>
-  </si>
-  <si>
-    <t>Developed countries</t>
-  </si>
-  <si>
-    <t>Least developed countries</t>
-  </si>
-  <si>
-    <t>Landlocked developing countries</t>
-  </si>
-  <si>
-    <t>Small island developing States</t>
-  </si>
-  <si>
-    <t>PES (GtCO2/year)</t>
-  </si>
-  <si>
-    <t>COP 27 Announcement (GtCO2/year)</t>
-  </si>
-  <si>
-    <t>COP 28 Announcement (GtCO2/year)</t>
-  </si>
-  <si>
-    <t>1.5°C Scenario (GtCO2/year)</t>
   </si>
 </sst>
 </file>
@@ -654,7 +700,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,6 +726,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -730,7 +784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -741,6 +795,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1075,10 +1130,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:G79"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="7" max="7" width="32.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1101,7 +1168,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1124,7 +1191,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1147,7 +1214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1170,7 +1237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1193,7 +1260,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1216,7 +1283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1239,7 +1306,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1262,7 +1329,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1285,7 +1352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1308,7 +1375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -1331,7 +1398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -1354,7 +1421,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -1377,7 +1444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -1400,7 +1467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -1423,7 +1490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -1446,7 +1513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -1469,7 +1536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -1492,7 +1559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -1515,7 +1582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -1538,7 +1605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -1561,7 +1628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -1584,7 +1651,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
@@ -1607,7 +1674,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
@@ -1630,7 +1697,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
@@ -1653,7 +1720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
         <v>57</v>
       </c>
@@ -1676,7 +1743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -1699,7 +1766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
         <v>61</v>
       </c>
@@ -1722,7 +1789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
         <v>63</v>
       </c>
@@ -1745,7 +1812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
@@ -1768,7 +1835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
         <v>67</v>
       </c>
@@ -1791,7 +1858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
         <v>69</v>
       </c>
@@ -1814,7 +1881,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
         <v>71</v>
       </c>
@@ -1837,7 +1904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7">
       <c r="A34" s="1" t="s">
         <v>73</v>
       </c>
@@ -1860,7 +1927,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
         <v>76</v>
       </c>
@@ -1883,7 +1950,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
         <v>78</v>
       </c>
@@ -1906,7 +1973,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
         <v>80</v>
       </c>
@@ -1929,7 +1996,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
         <v>82</v>
       </c>
@@ -1952,7 +2019,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
         <v>84</v>
       </c>
@@ -1975,7 +2042,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
         <v>86</v>
       </c>
@@ -1998,7 +2065,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
         <v>88</v>
       </c>
@@ -2021,7 +2088,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
         <v>90</v>
       </c>
@@ -2044,7 +2111,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
         <v>92</v>
       </c>
@@ -2067,7 +2134,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7">
       <c r="A44" s="1" t="s">
         <v>94</v>
       </c>
@@ -2090,7 +2157,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7">
       <c r="A45" s="1" t="s">
         <v>96</v>
       </c>
@@ -2113,7 +2180,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7">
       <c r="A46" s="1" t="s">
         <v>98</v>
       </c>
@@ -2136,7 +2203,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
         <v>100</v>
       </c>
@@ -2159,7 +2226,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7">
       <c r="A48" s="1" t="s">
         <v>102</v>
       </c>
@@ -2182,7 +2249,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7">
       <c r="A49" s="1" t="s">
         <v>104</v>
       </c>
@@ -2205,7 +2272,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7">
       <c r="A50" s="1" t="s">
         <v>106</v>
       </c>
@@ -2228,7 +2295,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7">
       <c r="A51" s="1" t="s">
         <v>108</v>
       </c>
@@ -2251,7 +2318,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7">
       <c r="A52" s="1" t="s">
         <v>110</v>
       </c>
@@ -2274,7 +2341,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7">
       <c r="A53" s="1" t="s">
         <v>112</v>
       </c>
@@ -2297,7 +2364,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7">
       <c r="A54" s="1" t="s">
         <v>114</v>
       </c>
@@ -2320,7 +2387,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7">
       <c r="A55" s="1" t="s">
         <v>116</v>
       </c>
@@ -2343,7 +2410,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7">
       <c r="A56" s="1" t="s">
         <v>118</v>
       </c>
@@ -2366,7 +2433,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7">
       <c r="A57" s="1" t="s">
         <v>120</v>
       </c>
@@ -2389,7 +2456,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7">
       <c r="A58" s="1" t="s">
         <v>122</v>
       </c>
@@ -2412,7 +2479,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:7">
       <c r="A59" s="1" t="s">
         <v>124</v>
       </c>
@@ -2435,7 +2502,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7">
       <c r="A60" s="1" t="s">
         <v>126</v>
       </c>
@@ -2458,7 +2525,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7">
       <c r="A61" s="1" t="s">
         <v>128</v>
       </c>
@@ -2481,7 +2548,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7">
       <c r="A62" s="1" t="s">
         <v>130</v>
       </c>
@@ -2504,7 +2571,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7">
       <c r="A63" s="1" t="s">
         <v>132</v>
       </c>
@@ -2527,7 +2594,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:7">
       <c r="A64" s="1" t="s">
         <v>134</v>
       </c>
@@ -2550,7 +2617,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:7">
       <c r="A65" s="1" t="s">
         <v>136</v>
       </c>
@@ -2573,7 +2640,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:7">
       <c r="A66" s="1" t="s">
         <v>138</v>
       </c>
@@ -2596,7 +2663,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7">
       <c r="A67" s="1" t="s">
         <v>140</v>
       </c>
@@ -2619,7 +2686,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7">
       <c r="A68" s="1" t="s">
         <v>143</v>
       </c>
@@ -2642,7 +2709,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:7">
       <c r="A69" s="1" t="s">
         <v>145</v>
       </c>
@@ -2665,7 +2732,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:7">
       <c r="A70" s="1" t="s">
         <v>148</v>
       </c>
@@ -2688,7 +2755,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7">
       <c r="A71" s="1" t="s">
         <v>150</v>
       </c>
@@ -2711,7 +2778,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7">
       <c r="A72" s="1" t="s">
         <v>152</v>
       </c>
@@ -2734,7 +2801,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7">
       <c r="A73" s="1" t="s">
         <v>154</v>
       </c>
@@ -2757,7 +2824,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7">
       <c r="A74" s="1" t="s">
         <v>156</v>
       </c>
@@ -2780,7 +2847,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7">
       <c r="A75" s="1" t="s">
         <v>158</v>
       </c>
@@ -2803,7 +2870,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7">
       <c r="A76" s="1" t="s">
         <v>160</v>
       </c>
@@ -2826,7 +2893,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7">
       <c r="A77" s="1" t="s">
         <v>162</v>
       </c>
@@ -2849,7 +2916,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:7">
       <c r="A78" s="1" t="s">
         <v>164</v>
       </c>
@@ -2872,7 +2939,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:7">
       <c r="A79" s="1" t="s">
         <v>167</v>
       </c>
@@ -2893,6 +2960,119 @@
       </c>
       <c r="G79" s="1" t="s">
         <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEBE8162-9761-41C4-99BB-0B5C96BD150F}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1">
+        <v>2015</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="3">
+        <v>16.7</v>
+      </c>
+      <c r="C2" s="3">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="3">
+        <v>22.9</v>
+      </c>
+      <c r="C5" s="3">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="3">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="3">
+        <v>13.7</v>
+      </c>
+      <c r="C9" s="3">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2902,16 +3082,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBA9ACB-4A6F-4733-A934-7EEB633D3300}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:G125"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.86328125" customWidth="1"/>
-    <col min="2" max="2" width="19.265625" customWidth="1"/>
-    <col min="3" max="3" width="24.73046875" customWidth="1"/>
-    <col min="7" max="7" width="9.1328125" style="3"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2922,7 +3105,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1899</v>
       </c>
@@ -2930,7 +3113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1900</v>
       </c>
@@ -2941,7 +3124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>1901</v>
       </c>
@@ -2952,7 +3135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>1902</v>
       </c>
@@ -2963,7 +3146,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>1903</v>
       </c>
@@ -2974,7 +3157,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>1904</v>
       </c>
@@ -2985,7 +3168,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>1905</v>
       </c>
@@ -2996,7 +3179,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>1906</v>
       </c>
@@ -3007,7 +3190,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>1907</v>
       </c>
@@ -3018,7 +3201,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>1908</v>
       </c>
@@ -3029,7 +3212,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>1909</v>
       </c>
@@ -3040,7 +3223,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>1910</v>
       </c>
@@ -3051,7 +3234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>1911</v>
       </c>
@@ -3062,7 +3245,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>1912</v>
       </c>
@@ -3073,7 +3256,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>1913</v>
       </c>
@@ -3084,7 +3267,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>1914</v>
       </c>
@@ -3095,7 +3278,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>1915</v>
       </c>
@@ -3106,7 +3289,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>1916</v>
       </c>
@@ -3117,7 +3300,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>1917</v>
       </c>
@@ -3128,7 +3311,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>1918</v>
       </c>
@@ -3139,7 +3322,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>1919</v>
       </c>
@@ -3150,7 +3333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>1920</v>
       </c>
@@ -3161,7 +3344,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>1921</v>
       </c>
@@ -3172,7 +3355,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>1922</v>
       </c>
@@ -3183,7 +3366,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>1923</v>
       </c>
@@ -3194,7 +3377,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>1924</v>
       </c>
@@ -3205,7 +3388,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>1925</v>
       </c>
@@ -3216,7 +3399,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>1926</v>
       </c>
@@ -3227,7 +3410,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>1927</v>
       </c>
@@ -3238,7 +3421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>1928</v>
       </c>
@@ -3249,7 +3432,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3">
       <c r="A32">
         <v>1929</v>
       </c>
@@ -3260,7 +3443,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>1930</v>
       </c>
@@ -3271,7 +3454,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>1931</v>
       </c>
@@ -3282,7 +3465,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>1932</v>
       </c>
@@ -3293,7 +3476,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>1933</v>
       </c>
@@ -3304,7 +3487,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>1934</v>
       </c>
@@ -3315,7 +3498,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>1935</v>
       </c>
@@ -3326,7 +3509,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>1936</v>
       </c>
@@ -3337,7 +3520,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>1937</v>
       </c>
@@ -3348,7 +3531,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>1938</v>
       </c>
@@ -3359,7 +3542,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>1939</v>
       </c>
@@ -3370,7 +3553,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>1940</v>
       </c>
@@ -3381,7 +3564,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>1941</v>
       </c>
@@ -3392,7 +3575,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>1942</v>
       </c>
@@ -3403,7 +3586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>1943</v>
       </c>
@@ -3414,7 +3597,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>1944</v>
       </c>
@@ -3425,7 +3608,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>1945</v>
       </c>
@@ -3436,7 +3619,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>1946</v>
       </c>
@@ -3447,7 +3630,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>1947</v>
       </c>
@@ -3458,7 +3641,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3">
       <c r="A51">
         <v>1948</v>
       </c>
@@ -3469,7 +3652,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>1949</v>
       </c>
@@ -3480,7 +3663,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>1950</v>
       </c>
@@ -3491,7 +3674,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>1951</v>
       </c>
@@ -3502,7 +3685,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>1952</v>
       </c>
@@ -3513,7 +3696,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>1953</v>
       </c>
@@ -3524,7 +3707,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>1954</v>
       </c>
@@ -3535,7 +3718,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>1955</v>
       </c>
@@ -3546,7 +3729,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>1956</v>
       </c>
@@ -3557,7 +3740,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>1957</v>
       </c>
@@ -3568,7 +3751,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>1958</v>
       </c>
@@ -3579,7 +3762,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>1959</v>
       </c>
@@ -3590,7 +3773,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>1960</v>
       </c>
@@ -3601,7 +3784,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>1961</v>
       </c>
@@ -3612,7 +3795,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>1962</v>
       </c>
@@ -3623,7 +3806,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>1963</v>
       </c>
@@ -3634,7 +3817,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>1964</v>
       </c>
@@ -3645,7 +3828,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>1965</v>
       </c>
@@ -3656,7 +3839,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>1966</v>
       </c>
@@ -3667,7 +3850,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>1967</v>
       </c>
@@ -3678,7 +3861,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>1968</v>
       </c>
@@ -3689,7 +3872,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:3">
       <c r="A72">
         <v>1969</v>
       </c>
@@ -3700,7 +3883,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:3">
       <c r="A73">
         <v>1970</v>
       </c>
@@ -3711,7 +3894,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3">
       <c r="A74">
         <v>1971</v>
       </c>
@@ -3722,7 +3905,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3">
       <c r="A75">
         <v>1972</v>
       </c>
@@ -3733,7 +3916,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>1973</v>
       </c>
@@ -3744,7 +3927,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3">
       <c r="A77">
         <v>1974</v>
       </c>
@@ -3755,7 +3938,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3">
       <c r="A78">
         <v>1975</v>
       </c>
@@ -3766,7 +3949,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>1976</v>
       </c>
@@ -3777,7 +3960,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:3">
       <c r="A80">
         <v>1977</v>
       </c>
@@ -3788,7 +3971,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:3">
       <c r="A81">
         <v>1978</v>
       </c>
@@ -3799,7 +3982,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:3">
       <c r="A82">
         <v>1979</v>
       </c>
@@ -3810,7 +3993,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:3">
       <c r="A83">
         <v>1980</v>
       </c>
@@ -3821,7 +4004,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:3">
       <c r="A84">
         <v>1981</v>
       </c>
@@ -3832,7 +4015,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:3">
       <c r="A85">
         <v>1982</v>
       </c>
@@ -3843,7 +4026,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:3">
       <c r="A86">
         <v>1983</v>
       </c>
@@ -3854,7 +4037,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:3">
       <c r="A87">
         <v>1984</v>
       </c>
@@ -3865,7 +4048,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:3">
       <c r="A88">
         <v>1985</v>
       </c>
@@ -3876,7 +4059,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:3">
       <c r="A89">
         <v>1986</v>
       </c>
@@ -3887,7 +4070,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:3">
       <c r="A90">
         <v>1987</v>
       </c>
@@ -3898,7 +4081,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:3">
       <c r="A91">
         <v>1988</v>
       </c>
@@ -3909,7 +4092,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:3">
       <c r="A92">
         <v>1989</v>
       </c>
@@ -3920,7 +4103,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:3">
       <c r="A93">
         <v>1990</v>
       </c>
@@ -3931,7 +4114,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:3">
       <c r="A94">
         <v>1991</v>
       </c>
@@ -3942,7 +4125,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:3">
       <c r="A95">
         <v>1992</v>
       </c>
@@ -3953,7 +4136,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:3">
       <c r="A96">
         <v>1993</v>
       </c>
@@ -3964,7 +4147,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3">
       <c r="A97">
         <v>1994</v>
       </c>
@@ -3975,7 +4158,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:3">
       <c r="A98">
         <v>1995</v>
       </c>
@@ -3986,7 +4169,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3">
       <c r="A99">
         <v>1996</v>
       </c>
@@ -3997,7 +4180,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:3">
       <c r="A100">
         <v>1997</v>
       </c>
@@ -4008,7 +4191,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:3">
       <c r="A101">
         <v>1998</v>
       </c>
@@ -4019,7 +4202,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3">
       <c r="A102">
         <v>1999</v>
       </c>
@@ -4030,7 +4213,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:3">
       <c r="A103">
         <v>2000</v>
       </c>
@@ -4041,7 +4224,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:3">
       <c r="A104">
         <v>2001</v>
       </c>
@@ -4052,7 +4235,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:3">
       <c r="A105">
         <v>2002</v>
       </c>
@@ -4063,7 +4246,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:3">
       <c r="A106">
         <v>2003</v>
       </c>
@@ -4074,7 +4257,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:3">
       <c r="A107">
         <v>2004</v>
       </c>
@@ -4085,7 +4268,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:3">
       <c r="A108">
         <v>2005</v>
       </c>
@@ -4096,7 +4279,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:3">
       <c r="A109">
         <v>2006</v>
       </c>
@@ -4107,7 +4290,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:3">
       <c r="A110">
         <v>2007</v>
       </c>
@@ -4118,7 +4301,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:3">
       <c r="A111">
         <v>2008</v>
       </c>
@@ -4129,7 +4312,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:3">
       <c r="A112">
         <v>2009</v>
       </c>
@@ -4140,7 +4323,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:3">
       <c r="A113">
         <v>2010</v>
       </c>
@@ -4151,7 +4334,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:3">
       <c r="A114">
         <v>2011</v>
       </c>
@@ -4162,7 +4345,7 @@
         <v>33.6</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:3">
       <c r="A115">
         <v>2012</v>
       </c>
@@ -4173,7 +4356,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:3">
       <c r="A116">
         <v>2013</v>
       </c>
@@ -4184,7 +4367,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:3">
       <c r="A117">
         <v>2014</v>
       </c>
@@ -4195,7 +4378,7 @@
         <v>34.9</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:3">
       <c r="A118">
         <v>2015</v>
       </c>
@@ -4206,7 +4389,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:3">
       <c r="A119">
         <v>2016</v>
       </c>
@@ -4217,7 +4400,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:3">
       <c r="A120">
         <v>2017</v>
       </c>
@@ -4228,7 +4411,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:3">
       <c r="A121">
         <v>2018</v>
       </c>
@@ -4239,7 +4422,7 @@
         <v>36.299999999999997</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:3">
       <c r="A122">
         <v>2019</v>
       </c>
@@ -4250,7 +4433,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:3">
       <c r="A123">
         <v>2020</v>
       </c>
@@ -4261,7 +4444,7 @@
         <v>34.299999999999997</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:3">
       <c r="A124">
         <v>2021</v>
       </c>
@@ -4272,7 +4455,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:3">
       <c r="A125">
         <v>2022</v>
       </c>
@@ -4290,13 +4473,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15EBE575-8FC5-4FC5-BC4F-031576FFFEC9}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.265625" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>171</v>
       </c>
@@ -4307,7 +4493,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>173</v>
       </c>
@@ -4318,7 +4504,7 @@
         <v>3054.94</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>175</v>
       </c>
@@ -4329,7 +4515,7 @@
         <v>16302.19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>176</v>
       </c>
@@ -4340,7 +4526,7 @@
         <v>3232.45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>177</v>
       </c>
@@ -4351,7 +4537,7 @@
         <v>6384.05</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>178</v>
       </c>
@@ -4362,7 +4548,7 @@
         <v>599.07000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>179</v>
       </c>
@@ -4380,13 +4566,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F716C0-9C27-44B9-8112-074EFB2949C9}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="9.73046875" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -4400,7 +4589,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4">
       <c r="A2" s="6">
         <v>1800</v>
       </c>
@@ -4410,7 +4599,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4">
       <c r="A3" s="6">
         <v>1820</v>
       </c>
@@ -4420,7 +4609,7 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4">
       <c r="A4" s="6">
         <v>1840</v>
       </c>
@@ -4430,7 +4619,7 @@
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4">
       <c r="A5" s="6">
         <v>1860</v>
       </c>
@@ -4440,7 +4629,7 @@
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4">
       <c r="A6" s="6">
         <v>1880</v>
       </c>
@@ -4450,7 +4639,7 @@
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4">
       <c r="A7" s="6">
         <v>1900</v>
       </c>
@@ -4460,7 +4649,7 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4">
       <c r="A8" s="6">
         <v>1920</v>
       </c>
@@ -4470,7 +4659,7 @@
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4">
       <c r="A9" s="6">
         <v>1940</v>
       </c>
@@ -4480,7 +4669,7 @@
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4">
       <c r="A10" s="6">
         <v>1950</v>
       </c>
@@ -4490,7 +4679,7 @@
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4">
       <c r="A11" s="6">
         <v>1960</v>
       </c>
@@ -4500,7 +4689,7 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4">
       <c r="A12" s="6">
         <v>1970</v>
       </c>
@@ -4510,7 +4699,7 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4">
       <c r="A13" s="6">
         <v>1980</v>
       </c>
@@ -4520,7 +4709,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4">
       <c r="A14" s="6">
         <v>1990</v>
       </c>
@@ -4530,7 +4719,7 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4">
       <c r="A15" s="6">
         <v>2000</v>
       </c>
@@ -4542,7 +4731,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4">
       <c r="A16" s="6">
         <v>2010</v>
       </c>
@@ -4554,7 +4743,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4">
       <c r="A17" s="6">
         <v>2020</v>
       </c>
@@ -4566,7 +4755,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4">
       <c r="A18" s="6">
         <v>2023</v>
       </c>
@@ -4578,7 +4767,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4">
       <c r="A19" s="6">
         <v>2025</v>
       </c>
@@ -4590,7 +4779,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4">
       <c r="A20" s="6">
         <v>2030</v>
       </c>
@@ -4602,7 +4791,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4">
       <c r="A21" s="6">
         <v>2035</v>
       </c>
@@ -4614,7 +4803,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4">
       <c r="A22" s="6">
         <v>2040</v>
       </c>
@@ -4626,7 +4815,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4">
       <c r="A23" s="6">
         <v>2050</v>
       </c>
@@ -4645,13 +4834,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51512212-8C59-4042-8F2D-4ECB2FD3960F}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.265625" customWidth="1"/>
+    <col min="1" max="1" width="61" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>183</v>
       </c>
@@ -4662,7 +4855,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>184</v>
       </c>
@@ -4673,7 +4866,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3">
       <c r="A3" s="7" t="s">
         <v>185</v>
       </c>
@@ -4684,7 +4877,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3">
       <c r="A4" s="7" t="s">
         <v>186</v>
       </c>
@@ -4695,7 +4888,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>187</v>
       </c>
@@ -4706,7 +4899,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>188</v>
       </c>
@@ -4717,7 +4910,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>189</v>
       </c>
@@ -4728,9 +4921,9 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B8" s="3">
         <v>9.3000000000000007</v>
@@ -4739,9 +4932,9 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B9" s="3">
         <v>13.7</v>
@@ -4757,25 +4950,29 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E607DCC-89F6-4115-90EA-DC7FC3D82AE3}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.59765625" customWidth="1"/>
-    <col min="3" max="4" width="19.59765625" customWidth="1"/>
+    <col min="1" max="1" width="32.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" customWidth="1"/>
+    <col min="3" max="4" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>183</v>
       </c>
-      <c r="B1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B1">
+        <v>2015</v>
+      </c>
+      <c r="C1">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>192</v>
       </c>
@@ -4786,7 +4983,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>193</v>
       </c>
@@ -4797,7 +4994,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>194</v>
       </c>
@@ -4808,7 +5005,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>195</v>
       </c>
@@ -4819,7 +5016,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>196</v>
       </c>
@@ -4830,7 +5027,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>180</v>
       </c>
@@ -4848,14 +5045,18 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B78EA1-4B37-4E79-B5FA-0A9AC330BC2E}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="17.3984375" customWidth="1"/>
-    <col min="5" max="7" width="32.86328125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" customWidth="1"/>
+    <col min="5" max="7" width="32.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4872,39 +5073,188 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>2022</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2030</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>2035</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>2040</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>2045</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>2050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{346E3136-1948-48AF-99EE-E205DD883628}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3">
+        <v>0.18099999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5">
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7">
+        <v>0.124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C728FFA5-AFFE-486A-A4EB-531536CE0076}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2">
+        <v>0.15</v>
+      </c>
+      <c r="C2">
+        <v>1.29</v>
+      </c>
+      <c r="D2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C3">
+        <v>1.46</v>
+      </c>
+      <c r="D3">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4">
+        <v>0.04</v>
+      </c>
+      <c r="C4">
+        <v>1.04</v>
+      </c>
+      <c r="D4">
+        <v>0.94</v>
       </c>
     </row>
   </sheetData>
@@ -4913,14 +5263,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5165,48 +5513,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7E9460-F128-4419-BA1C-5413CC6C046F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7E9460-F128-4419-BA1C-5413CC6C046F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}"/>
 </file>
--- a/02_Inputs/Data/Charts/Module 1 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 1 - Datasets for Charts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29012"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="585" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5BA57CD-7C89-46B4-8856-171F83B73066}"/>
+  <xr:revisionPtr revIDLastSave="593" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75F7A435-F934-41D7-8D50-C9EC5FF8F9E0}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="9" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M1_C1_2" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="212">
   <si>
     <t>ISO Code</t>
   </si>
@@ -594,13 +594,7 @@
     <t>Category</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy Consumption: Total </t>
-  </si>
-  <si>
-    <t>Final Energy Consumption: Modern renewable sources</t>
-  </si>
-  <si>
-    <t>Final Energy Consumption: Traditional use of biomass</t>
+    <t>Final Energy Consumption</t>
   </si>
   <si>
     <t>Electricity</t>
@@ -609,13 +603,7 @@
     <t>Transport</t>
   </si>
   <si>
-    <t>Heat: Total</t>
-  </si>
-  <si>
-    <t>Heat: Modern renewable sources</t>
-  </si>
-  <si>
-    <t>Heat: Traditional use of biomass</t>
+    <t>Heat</t>
   </si>
   <si>
     <t>Developing countries</t>
@@ -688,9 +676,6 @@
   </si>
   <si>
     <t>Traditional use of biomass</t>
-  </si>
-  <si>
-    <t>Heat</t>
   </si>
 </sst>
 </file>
@@ -2989,7 +2974,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B2" s="3">
         <v>16.7</v>
@@ -3000,7 +2985,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B3" s="3">
         <v>10</v>
@@ -3011,7 +2996,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3">
         <v>6.7</v>
@@ -3022,7 +3007,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B5" s="3">
         <v>22.9</v>
@@ -3033,7 +3018,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B6" s="3">
         <v>3.5</v>
@@ -3044,7 +3029,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="B7" s="3">
         <v>23</v>
@@ -3055,7 +3040,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B8" s="3">
         <v>9.3000000000000007</v>
@@ -3066,7 +3051,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B9" s="3">
         <v>13.7</v>
@@ -4867,25 +4852,25 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" t="s">
         <v>185</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>22.9</v>
       </c>
       <c r="C3" s="3">
-        <v>12.5</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" t="s">
         <v>186</v>
       </c>
       <c r="B4" s="3">
-        <v>6.7</v>
+        <v>3.5</v>
       </c>
       <c r="C4" s="3">
-        <v>6.2</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4893,55 +4878,21 @@
         <v>187</v>
       </c>
       <c r="B5" s="3">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3">
-        <v>28.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="C6" s="3">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="3">
-        <v>23</v>
-      </c>
-      <c r="C7" s="3">
         <v>23.5</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="3">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="C8" s="3">
-        <v>10.5</v>
-      </c>
+      <c r="A8" s="7"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B9" s="3">
-        <v>13.7</v>
-      </c>
-      <c r="C9" s="3">
-        <v>13</v>
-      </c>
+      <c r="A9" s="7"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4974,7 +4925,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B2">
         <v>155</v>
@@ -4985,7 +4936,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B3">
         <v>691</v>
@@ -4996,7 +4947,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B4">
         <v>27</v>
@@ -5007,7 +4958,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B5">
         <v>86</v>
@@ -5018,7 +4969,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B6">
         <v>54</v>
@@ -5061,16 +5012,16 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5127,16 +5078,16 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B2">
         <v>0.22</v>
@@ -5144,7 +5095,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B3">
         <v>0.18099999999999999</v>
@@ -5152,7 +5103,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B4">
         <v>9.9000000000000005E-2</v>
@@ -5168,7 +5119,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B6">
         <v>7.4999999999999997E-2</v>
@@ -5176,7 +5127,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B7">
         <v>0.124</v>
@@ -5203,21 +5154,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B2">
         <v>0.15</v>
@@ -5231,7 +5182,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B3">
         <v>0.28000000000000003</v>
@@ -5245,7 +5196,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B4">
         <v>0.04</v>
@@ -5263,15 +5214,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -5512,6 +5454,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5524,11 +5475,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7E9460-F128-4419-BA1C-5413CC6C046F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7E9460-F128-4419-BA1C-5413CC6C046F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/02_Inputs/Data/Charts/Module 1 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 1 - Datasets for Charts.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29019"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1060" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{047DF3C6-2642-4B9E-99E0-7FF3CB97C5F1}"/>
+  <xr:revisionPtr revIDLastSave="1063" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4241459D-97D3-4140-B6E7-C0875ECE6649}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="18" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="340">
   <si>
     <t>ISO Code</t>
   </si>
@@ -800,90 +800,6 @@
   </si>
   <si>
     <t>Low-impact</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>1,3</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>2,6</t>
-  </si>
-  <si>
-    <t>2,0</t>
-  </si>
-  <si>
-    <t>4,0</t>
-  </si>
-  <si>
-    <t>3,0</t>
-  </si>
-  <si>
-    <t>5,4</t>
-  </si>
-  <si>
-    <t>2,7</t>
-  </si>
-  <si>
-    <t>6,8</t>
-  </si>
-  <si>
-    <t>5,1</t>
-  </si>
-  <si>
-    <t>3,4</t>
-  </si>
-  <si>
-    <t>8,3</t>
-  </si>
-  <si>
-    <t>6,2</t>
-  </si>
-  <si>
-    <t>4,1</t>
-  </si>
-  <si>
-    <t>9,9</t>
-  </si>
-  <si>
-    <t>7,4</t>
-  </si>
-  <si>
-    <t>4,9</t>
-  </si>
-  <si>
-    <t>11,5</t>
-  </si>
-  <si>
-    <t>8,5</t>
-  </si>
-  <si>
-    <t>5,6</t>
-  </si>
-  <si>
-    <t>13,2</t>
-  </si>
-  <si>
-    <t>9,8</t>
-  </si>
-  <si>
-    <t>6,4</t>
-  </si>
-  <si>
-    <t>14,9</t>
-  </si>
-  <si>
-    <t>11,0</t>
-  </si>
-  <si>
-    <t>7,2</t>
   </si>
   <si>
     <t>Crude oil</t>
@@ -7141,154 +7057,154 @@
       <c r="A2" s="12">
         <v>2020</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>249</v>
+      <c r="B2" s="12">
+        <v>0</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0</v>
+      </c>
+      <c r="D2" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="12">
         <v>2021</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>252</v>
+      <c r="B3" s="12">
+        <v>1.3</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1</v>
+      </c>
+      <c r="D3" s="12">
+        <v>0.6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12">
         <v>2022</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>250</v>
+      <c r="B4" s="12">
+        <v>2.6</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1.3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="12">
         <v>2023</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>254</v>
+      <c r="B5" s="12">
+        <v>4</v>
+      </c>
+      <c r="C5" s="12">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12">
         <v>2024</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>258</v>
+      <c r="B6" s="12">
+        <v>5.4</v>
+      </c>
+      <c r="C6" s="12">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12">
+        <v>2.7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12">
         <v>2025</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>261</v>
+      <c r="B7" s="12">
+        <v>6.8</v>
+      </c>
+      <c r="C7" s="12">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D7" s="12">
+        <v>3.4</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12">
         <v>2026</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>264</v>
+      <c r="B8" s="12">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="C8" s="12">
+        <v>6.2</v>
+      </c>
+      <c r="D8" s="12">
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12">
         <v>2027</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>267</v>
+      <c r="B9" s="12">
+        <v>9.9</v>
+      </c>
+      <c r="C9" s="12">
+        <v>7.4</v>
+      </c>
+      <c r="D9" s="12">
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12">
         <v>2028</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>270</v>
+      <c r="B10" s="12">
+        <v>11.5</v>
+      </c>
+      <c r="C10" s="12">
+        <v>8.5</v>
+      </c>
+      <c r="D10" s="12">
+        <v>5.6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="12">
         <v>2029</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>273</v>
+      <c r="B11" s="12">
+        <v>13.2</v>
+      </c>
+      <c r="C11" s="12">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D11" s="12">
+        <v>6.4</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="12">
         <v>2030</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>276</v>
+      <c r="B12" s="12">
+        <v>14.9</v>
+      </c>
+      <c r="C12" s="12">
+        <v>11</v>
+      </c>
+      <c r="D12" s="12">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -7314,10 +7230,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7328,7 +7244,7 @@
         <v>32329980</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7339,7 +7255,7 @@
         <v>25000780</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7350,18 +7266,18 @@
         <v>22884420</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="B5" s="6">
         <v>14114495</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7372,7 +7288,7 @@
         <v>12115194</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7383,7 +7299,7 @@
         <v>9447692</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7394,7 +7310,7 @@
         <v>8585257</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7405,7 +7321,7 @@
         <v>8497131</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7416,7 +7332,7 @@
         <v>6736710</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7427,7 +7343,7 @@
         <v>6455547</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7438,7 +7354,7 @@
         <v>6349888</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -7449,7 +7365,7 @@
         <v>4156856</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -7460,7 +7376,7 @@
         <v>3884442</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -7471,7 +7387,7 @@
         <v>3450562</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7482,7 +7398,7 @@
         <v>2998178</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7493,40 +7409,40 @@
         <v>2898238</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="B18" s="6">
         <v>2555025</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="B19" s="6">
         <v>2365729</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="B20" s="6">
         <v>2308096</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7537,7 +7453,7 @@
         <v>2230003</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7548,7 +7464,7 @@
         <v>1924685</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7559,7 +7475,7 @@
         <v>1702245</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7570,7 +7486,7 @@
         <v>1644715</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7581,7 +7497,7 @@
         <v>1442157</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7592,7 +7508,7 @@
         <v>1441109</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -7603,7 +7519,7 @@
         <v>1398689</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -7614,7 +7530,7 @@
         <v>1337492</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7625,7 +7541,7 @@
         <v>1322066</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7636,7 +7552,7 @@
         <v>1081614</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7647,7 +7563,7 @@
         <v>1058067</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7658,18 +7574,18 @@
         <v>806790</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="B33" s="6">
         <v>590740</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -7680,29 +7596,29 @@
         <v>548126</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="B35" s="6">
         <v>444369</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="B36" s="6">
         <v>431201</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -7713,7 +7629,7 @@
         <v>407449</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -7724,51 +7640,51 @@
         <v>398119</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="B39" s="6">
         <v>306589</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="B40" s="6">
         <v>300485</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="B41" s="6">
         <v>297264</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="B42" s="6">
         <v>226773</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7779,7 +7695,7 @@
         <v>209583</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7790,18 +7706,18 @@
         <v>201720</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="6" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="B45" s="6">
         <v>193215</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7812,7 +7728,7 @@
         <v>171371</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7823,7 +7739,7 @@
         <v>153357</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7834,18 +7750,18 @@
         <v>149221</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="6" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="B49" s="6">
         <v>148102</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7856,7 +7772,7 @@
         <v>137540</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7867,7 +7783,7 @@
         <v>136948</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7878,7 +7794,7 @@
         <v>127641</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7889,40 +7805,40 @@
         <v>118969</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="6" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="B54" s="6">
         <v>118162</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="6" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="B55" s="6">
         <v>107920</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="6" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="B56" s="6">
         <v>105543</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7933,40 +7849,40 @@
         <v>91851</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="6" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="B58" s="6">
         <v>82408</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="6" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="B59" s="6">
         <v>82059</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="6" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="B60" s="6">
         <v>75770</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -7977,18 +7893,18 @@
         <v>72726</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="6" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
       <c r="B62" s="6">
         <v>55972</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7999,18 +7915,18 @@
         <v>51780</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="6" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="B64" s="6">
         <v>48033</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -8021,7 +7937,7 @@
         <v>45339</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -8032,7 +7948,7 @@
         <v>45142</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -8043,7 +7959,7 @@
         <v>39217</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -8054,40 +7970,40 @@
         <v>38350</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="6" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="B69" s="6">
         <v>36873</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="6" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="B70" s="6">
         <v>36634</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="6" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="B71" s="6">
         <v>34969</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -8098,7 +8014,7 @@
         <v>32815</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -8109,29 +8025,29 @@
         <v>30865</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="6" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="B74" s="6">
         <v>27524</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="6" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="B75" s="6">
         <v>26780</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -8142,7 +8058,7 @@
         <v>25406</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -8153,18 +8069,18 @@
         <v>21920</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="6" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="B78" s="6">
         <v>18230</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -8175,18 +8091,18 @@
         <v>16344</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="6" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="B80" s="6">
         <v>14816</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -8197,29 +8113,29 @@
         <v>14212</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="6" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="B82" s="6">
         <v>13369</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="6" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="B83" s="6">
         <v>12416</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -8230,18 +8146,18 @@
         <v>9949</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="6" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="B85" s="6">
         <v>8360</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -8252,7 +8168,7 @@
         <v>8004</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -8263,7 +8179,7 @@
         <v>7687</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -8274,18 +8190,18 @@
         <v>4849</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="6" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="B89" s="6">
         <v>1555</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -8296,7 +8212,7 @@
         <v>1201</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -8307,29 +8223,29 @@
         <v>1144</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="6" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="B92" s="6">
         <v>1047</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="6" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="B93" s="6">
         <v>540</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -8340,18 +8256,18 @@
         <v>353</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="6" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="B95" s="6">
         <v>197</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -8362,7 +8278,7 @@
         <v>93</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -8373,7 +8289,7 @@
         <v>38</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -8384,7 +8300,7 @@
         <v>6</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -8395,7 +8311,7 @@
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -8406,7 +8322,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -8417,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -8428,18 +8344,18 @@
         <v>0</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="6" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="B103" s="6">
         <v>0</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -8450,7 +8366,7 @@
         <v>0</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -8461,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -8472,7 +8388,7 @@
         <v>0</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -8483,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -8494,7 +8410,7 @@
         <v>0</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -8505,7 +8421,7 @@
         <v>0</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -8529,7 +8445,7 @@
         <v>185</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8540,7 +8456,7 @@
         <v>237763</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8551,7 +8467,7 @@
         <v>209398</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8562,7 +8478,7 @@
         <v>91231</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8573,370 +8489,370 @@
         <v>42722</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="B6" s="6">
         <v>37915</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="B7" s="6">
         <v>35106</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="B8" s="6">
         <v>23167</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="B9" s="6">
         <v>21422</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="B10" s="6">
         <v>19558</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="B11" s="6">
         <v>19475</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="B12" s="6">
         <v>17338</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="B13" s="6">
         <v>16539</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="B14" s="6">
         <v>15763</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="B15" s="6">
         <v>13250</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="B16" s="6">
         <v>12933</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
       <c r="B17" s="6">
         <v>12460</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="B18" s="6">
         <v>9974</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="B19" s="6">
         <v>9625</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="B20" s="6">
         <v>8706</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="B21" s="6">
         <v>7549</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="B22" s="6">
         <v>5775</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="B23" s="6">
         <v>5013</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="B24" s="6">
         <v>3192</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="B25" s="6">
         <v>3119</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="B26" s="6">
         <v>2613</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="B27" s="6">
         <v>2548</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="B28" s="6">
         <v>1669</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="B29" s="6">
         <v>1507</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="B30" s="6">
         <v>1331</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>329</v>
+        <v>301</v>
       </c>
       <c r="B31" s="6">
         <v>1101</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="B32" s="6">
         <v>1001</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="B33" s="6">
         <v>820</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="B34" s="6">
         <v>782</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="B35" s="6">
         <v>628</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="B36" s="6">
         <v>538</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="B37" s="6">
         <v>399</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="B38" s="6">
         <v>376</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -8960,7 +8876,7 @@
         <v>185</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8971,7 +8887,7 @@
         <v>8950643</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8982,7 +8898,7 @@
         <v>4495368</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8993,7 +8909,7 @@
         <v>1821867</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9004,7 +8920,7 @@
         <v>1151155</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -9015,18 +8931,18 @@
         <v>1017679</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="B7" s="6">
         <v>905136</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9037,7 +8953,7 @@
         <v>677371</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -9048,7 +8964,7 @@
         <v>658578</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9059,7 +8975,7 @@
         <v>624879</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9070,7 +8986,7 @@
         <v>578949</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9081,7 +8997,7 @@
         <v>473672</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9092,7 +9008,7 @@
         <v>418839</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9103,7 +9019,7 @@
         <v>397369</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9114,7 +9030,7 @@
         <v>367669</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9125,7 +9041,7 @@
         <v>346466</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9136,7 +9052,7 @@
         <v>328379</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9147,7 +9063,7 @@
         <v>325540</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9158,18 +9074,18 @@
         <v>292454</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="B20" s="6">
         <v>288153</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9180,7 +9096,7 @@
         <v>283961</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9191,7 +9107,7 @@
         <v>276416</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9202,7 +9118,7 @@
         <v>271531</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9213,7 +9129,7 @@
         <v>237763</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9224,7 +9140,7 @@
         <v>209398</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9235,7 +9151,7 @@
         <v>187298</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9246,7 +9162,7 @@
         <v>183187</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9257,7 +9173,7 @@
         <v>179748</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9268,7 +9184,7 @@
         <v>173159</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -9279,7 +9195,7 @@
         <v>172799</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9290,7 +9206,7 @@
         <v>155438</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -9301,7 +9217,7 @@
         <v>146730</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9312,7 +9228,7 @@
         <v>145645</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -9323,7 +9239,7 @@
         <v>133547</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9334,7 +9250,7 @@
         <v>121572</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -9345,7 +9261,7 @@
         <v>113552</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9356,7 +9272,7 @@
         <v>112294</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9367,7 +9283,7 @@
         <v>111515</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9378,7 +9294,7 @@
         <v>102348</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9389,7 +9305,7 @@
         <v>95947</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9400,7 +9316,7 @@
         <v>91231</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9411,7 +9327,7 @@
         <v>91019</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -9422,7 +9338,7 @@
         <v>85992</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9433,7 +9349,7 @@
         <v>84850</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -9444,7 +9360,7 @@
         <v>83544</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9455,7 +9371,7 @@
         <v>82424</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9466,7 +9382,7 @@
         <v>75964</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9477,7 +9393,7 @@
         <v>74269</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9488,7 +9404,7 @@
         <v>72186</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9499,7 +9415,7 @@
         <v>69193</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -9510,7 +9426,7 @@
         <v>65661</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -9521,7 +9437,7 @@
         <v>59777</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -9532,7 +9448,7 @@
         <v>57342</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -9543,7 +9459,7 @@
         <v>56002</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -9554,7 +9470,7 @@
         <v>54623</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -9565,18 +9481,18 @@
         <v>52670</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="6" t="s">
-        <v>334</v>
+        <v>306</v>
       </c>
       <c r="B57" s="6">
         <v>51031</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -9587,7 +9503,7 @@
         <v>50499</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -9598,7 +9514,7 @@
         <v>48807</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -9609,18 +9525,18 @@
         <v>44720</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="6" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="B61" s="6">
         <v>44109</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9631,7 +9547,7 @@
         <v>42771</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -9642,7 +9558,7 @@
         <v>42722</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -9653,18 +9569,18 @@
         <v>39400</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="6" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="B65" s="6">
         <v>37915</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -9675,7 +9591,7 @@
         <v>36097</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -9686,29 +9602,29 @@
         <v>35801</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="6" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="B68" s="6">
         <v>35647</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="6" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="B69" s="6">
         <v>35510</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -9719,18 +9635,18 @@
         <v>35123</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="6" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="B71" s="6">
         <v>35106</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -9741,7 +9657,7 @@
         <v>34045</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -9752,7 +9668,7 @@
         <v>33008</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -9763,7 +9679,7 @@
         <v>32600</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -9774,7 +9690,7 @@
         <v>29039</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -9785,73 +9701,73 @@
         <v>26838</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="6" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="B77" s="6">
         <v>23167</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="6" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="B78" s="6">
         <v>22557</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="6" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="B79" s="6">
         <v>21491</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="6" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="B80" s="6">
         <v>21422</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="6" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="B81" s="6">
         <v>21419</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="6" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="B82" s="6">
         <v>20918</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -9862,51 +9778,51 @@
         <v>20120</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="6" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="B84" s="6">
         <v>20061</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="6" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="B85" s="6">
         <v>19558</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="6" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="B86" s="6">
         <v>19475</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="6" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="B87" s="6">
         <v>17338</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -9917,73 +9833,73 @@
         <v>16576</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="6" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="B89" s="6">
         <v>16539</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="6" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="B90" s="6">
         <v>16384</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="6" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="B91" s="6">
         <v>15763</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="6" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="B92" s="6">
         <v>15616</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="6" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="B93" s="6">
         <v>14813</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="6" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="B94" s="6">
         <v>14246</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -9994,18 +9910,18 @@
         <v>14220</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="6" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="B96" s="6">
         <v>13882</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -10016,139 +9932,139 @@
         <v>13616</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="6" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="B98" s="6">
         <v>13296</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="6" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="B99" s="6">
         <v>13250</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="6" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="B100" s="6">
         <v>12933</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="6" t="s">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="B101" s="6">
         <v>12673</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="6" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
       <c r="B102" s="6">
         <v>12460</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="6" t="s">
-        <v>340</v>
+        <v>312</v>
       </c>
       <c r="B103" s="6">
         <v>12243</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="6" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="B104" s="6">
         <v>11408</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="6" t="s">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="B105" s="6">
         <v>11345</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="6" t="s">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="B106" s="6">
         <v>10691</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="6" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="B107" s="6">
         <v>10642</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="6" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="B108" s="6">
         <v>9974</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="6" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="B109" s="6">
         <v>9625</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -10159,18 +10075,18 @@
         <v>9493</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="6" t="s">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="B111" s="6">
         <v>9190</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -10181,73 +10097,73 @@
         <v>8936</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="6" t="s">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="B113" s="6">
         <v>8706</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="6" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="B114" s="6">
         <v>7750</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="6" t="s">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="B115" s="6">
         <v>7549</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="6" t="s">
-        <v>345</v>
+        <v>317</v>
       </c>
       <c r="B116" s="6">
         <v>7387</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="6" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="B117" s="6">
         <v>7002</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="6" t="s">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="B118" s="6">
         <v>6997</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -10258,40 +10174,40 @@
         <v>5942</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="6" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="B120" s="6">
         <v>5775</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="6" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="B121" s="6">
         <v>5602</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="6" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="B122" s="6">
         <v>5329</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -10302,7 +10218,7 @@
         <v>5267</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -10313,18 +10229,18 @@
         <v>5030</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="6" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="B125" s="6">
         <v>5013</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -10335,117 +10251,117 @@
         <v>4783</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="6" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="B127" s="6">
         <v>4439</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="6" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="B128" s="6">
         <v>4369</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="6" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="B129" s="6">
         <v>4333</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="6" t="s">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="B130" s="6">
         <v>3322</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="6" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="B131" s="6">
         <v>3192</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="6" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="B132" s="6">
         <v>3119</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="6" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="B133" s="6">
         <v>2613</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="6" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="B134" s="6">
         <v>2548</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="6" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="B135" s="6">
         <v>2544</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="6" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="B136" s="6">
         <v>2293</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -10456,172 +10372,172 @@
         <v>2258</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="6" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="B138" s="6">
         <v>2084</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="6" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="B139" s="6">
         <v>1669</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="6" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="B140" s="6">
         <v>1507</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="6" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="B141" s="6">
         <v>1331</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="6" t="s">
-        <v>329</v>
+        <v>301</v>
       </c>
       <c r="B142" s="6">
         <v>1101</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="6" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="B143" s="6">
         <v>1012</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="6" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="B144" s="6">
         <v>1001</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="6" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
       <c r="B145" s="6">
         <v>866</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="6" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="B146" s="6">
         <v>820</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="6" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="B147" s="6">
         <v>782</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="6" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="B148" s="6">
         <v>628</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="6" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="B149" s="6">
         <v>538</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="6" t="s">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="B150" s="6">
         <v>399</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="6" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="B151" s="6">
         <v>376</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="6" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="B152" s="6">
         <v>210</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -10651,13 +10567,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>355</v>
+        <v>327</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>225</v>
@@ -10666,7 +10582,7 @@
         <v>226</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:32">
@@ -12950,7 +12866,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="B2" s="3">
         <v>16.7</v>
@@ -12961,7 +12877,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="B3" s="3">
         <v>10</v>
@@ -12972,7 +12888,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3">
         <v>6.7</v>
@@ -13016,7 +12932,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="B8" s="3">
         <v>9.3000000000000007</v>
@@ -13027,7 +12943,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="B9" s="3">
         <v>13.7</v>
@@ -13048,13 +12964,13 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="C2" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="H2" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="N2" t="s">
-        <v>363</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="2:14">
@@ -13348,16 +13264,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
       <c r="A1" s="9" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75">
@@ -13371,7 +13287,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75">
@@ -13385,7 +13301,7 @@
         <v>2001</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75">
@@ -13399,7 +13315,7 @@
         <v>2002</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75">
@@ -13413,7 +13329,7 @@
         <v>2003</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75">
@@ -13427,7 +13343,7 @@
         <v>2004</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75">
@@ -13441,7 +13357,7 @@
         <v>2005</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75">
@@ -13455,7 +13371,7 @@
         <v>2006</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75">
@@ -13469,7 +13385,7 @@
         <v>2007</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75">
@@ -13483,7 +13399,7 @@
         <v>2008</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75">
@@ -13497,7 +13413,7 @@
         <v>2009</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75">
@@ -13511,7 +13427,7 @@
         <v>2010</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75">
@@ -13525,7 +13441,7 @@
         <v>2011</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75">
@@ -13539,7 +13455,7 @@
         <v>2012</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75">
@@ -13553,7 +13469,7 @@
         <v>2013</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75">
@@ -13567,7 +13483,7 @@
         <v>2014</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
@@ -13581,7 +13497,7 @@
         <v>2015</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75">
@@ -13595,7 +13511,7 @@
         <v>2016</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75">
@@ -13609,7 +13525,7 @@
         <v>2017</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75">
@@ -13623,7 +13539,7 @@
         <v>2018</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75">
@@ -13637,7 +13553,7 @@
         <v>2019</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75">
@@ -13651,7 +13567,7 @@
         <v>2020</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75">
@@ -13665,7 +13581,7 @@
         <v>2021</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75">
@@ -13679,7 +13595,7 @@
         <v>2022</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75">
@@ -13693,7 +13609,7 @@
         <v>2000</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75">
@@ -13707,7 +13623,7 @@
         <v>2001</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75">
@@ -13721,7 +13637,7 @@
         <v>2002</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75">
@@ -13735,7 +13651,7 @@
         <v>2003</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75">
@@ -13749,7 +13665,7 @@
         <v>2004</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75">
@@ -13763,7 +13679,7 @@
         <v>2005</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75">
@@ -13777,7 +13693,7 @@
         <v>2006</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75">
@@ -13791,7 +13707,7 @@
         <v>2007</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75">
@@ -13805,7 +13721,7 @@
         <v>2008</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75">
@@ -13819,7 +13735,7 @@
         <v>2009</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75">
@@ -13833,7 +13749,7 @@
         <v>2010</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75">
@@ -13847,7 +13763,7 @@
         <v>2011</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75">
@@ -13861,7 +13777,7 @@
         <v>2012</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75">
@@ -13875,7 +13791,7 @@
         <v>2013</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75">
@@ -13889,7 +13805,7 @@
         <v>2014</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75">
@@ -13903,7 +13819,7 @@
         <v>2015</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75">
@@ -13917,7 +13833,7 @@
         <v>2016</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75">
@@ -13931,7 +13847,7 @@
         <v>2017</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75">
@@ -13945,7 +13861,7 @@
         <v>2018</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75">
@@ -13959,7 +13875,7 @@
         <v>2019</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75">
@@ -13973,7 +13889,7 @@
         <v>2020</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.75">
@@ -13987,7 +13903,7 @@
         <v>2021</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75">
@@ -14001,7 +13917,7 @@
         <v>2022</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75">
@@ -14015,7 +13931,7 @@
         <v>2000</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75">
@@ -14029,7 +13945,7 @@
         <v>2001</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75">
@@ -14043,7 +13959,7 @@
         <v>2002</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75">
@@ -14057,7 +13973,7 @@
         <v>2003</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.75">
@@ -14071,7 +13987,7 @@
         <v>2004</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.75">
@@ -14085,7 +14001,7 @@
         <v>2005</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75">
@@ -14099,7 +14015,7 @@
         <v>2006</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75">
@@ -14113,7 +14029,7 @@
         <v>2007</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75">
@@ -14127,7 +14043,7 @@
         <v>2008</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75">
@@ -14141,7 +14057,7 @@
         <v>2009</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75">
@@ -14155,7 +14071,7 @@
         <v>2010</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75">
@@ -14169,7 +14085,7 @@
         <v>2011</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75">
@@ -14183,7 +14099,7 @@
         <v>2012</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75">
@@ -14197,7 +14113,7 @@
         <v>2013</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75">
@@ -14211,7 +14127,7 @@
         <v>2014</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75">
@@ -14225,7 +14141,7 @@
         <v>2015</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75">
@@ -14239,7 +14155,7 @@
         <v>2016</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75">
@@ -14253,7 +14169,7 @@
         <v>2017</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75">
@@ -14267,7 +14183,7 @@
         <v>2018</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75">
@@ -14281,7 +14197,7 @@
         <v>2019</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75">
@@ -14295,7 +14211,7 @@
         <v>2020</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75">
@@ -14309,7 +14225,7 @@
         <v>2021</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75">
@@ -14323,7 +14239,7 @@
         <v>2022</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75">
@@ -14337,7 +14253,7 @@
         <v>2000</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75">
@@ -14351,7 +14267,7 @@
         <v>2001</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75">
@@ -14365,7 +14281,7 @@
         <v>2002</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75">
@@ -14379,7 +14295,7 @@
         <v>2003</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75">
@@ -14393,7 +14309,7 @@
         <v>2004</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.75">
@@ -14407,7 +14323,7 @@
         <v>2005</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75">
@@ -14421,7 +14337,7 @@
         <v>2006</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.75">
@@ -14435,7 +14351,7 @@
         <v>2007</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.75">
@@ -14449,7 +14365,7 @@
         <v>2008</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.75">
@@ -14463,7 +14379,7 @@
         <v>2009</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75">
@@ -14477,7 +14393,7 @@
         <v>2010</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75">
@@ -14491,7 +14407,7 @@
         <v>2011</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75">
@@ -14505,7 +14421,7 @@
         <v>2012</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75">
@@ -14519,7 +14435,7 @@
         <v>2013</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75">
@@ -14533,7 +14449,7 @@
         <v>2014</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75">
@@ -14547,7 +14463,7 @@
         <v>2015</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75">
@@ -14561,7 +14477,7 @@
         <v>2016</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75">
@@ -14575,7 +14491,7 @@
         <v>2017</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75">
@@ -14589,7 +14505,7 @@
         <v>2018</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75">
@@ -14603,7 +14519,7 @@
         <v>2019</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75">
@@ -14617,7 +14533,7 @@
         <v>2020</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75">
@@ -14631,7 +14547,7 @@
         <v>2021</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75">
@@ -14645,7 +14561,7 @@
         <v>2022</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75">
@@ -14659,7 +14575,7 @@
         <v>2000</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75">
@@ -14673,7 +14589,7 @@
         <v>2001</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75">
@@ -14687,7 +14603,7 @@
         <v>2002</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75">
@@ -14701,7 +14617,7 @@
         <v>2003</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75">
@@ -14715,7 +14631,7 @@
         <v>2004</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75">
@@ -14729,7 +14645,7 @@
         <v>2005</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75">
@@ -14743,7 +14659,7 @@
         <v>2006</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75">
@@ -14757,7 +14673,7 @@
         <v>2007</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75">
@@ -14771,7 +14687,7 @@
         <v>2008</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75">
@@ -14785,7 +14701,7 @@
         <v>2009</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75">
@@ -14799,7 +14715,7 @@
         <v>2010</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75">
@@ -14813,7 +14729,7 @@
         <v>2011</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75">
@@ -14827,7 +14743,7 @@
         <v>2012</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75">
@@ -14841,7 +14757,7 @@
         <v>2013</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75">
@@ -14855,7 +14771,7 @@
         <v>2014</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75">
@@ -14869,7 +14785,7 @@
         <v>2015</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75">
@@ -14883,7 +14799,7 @@
         <v>2016</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75">
@@ -14897,7 +14813,7 @@
         <v>2017</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75">
@@ -14911,7 +14827,7 @@
         <v>2018</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75">
@@ -14925,7 +14841,7 @@
         <v>2019</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75">
@@ -14939,7 +14855,7 @@
         <v>2020</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75">
@@ -14953,7 +14869,7 @@
         <v>2021</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75">
@@ -14967,7 +14883,7 @@
         <v>2022</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75">
@@ -14981,7 +14897,7 @@
         <v>2000</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75">
@@ -14995,7 +14911,7 @@
         <v>2001</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75">
@@ -15009,7 +14925,7 @@
         <v>2002</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75">
@@ -15023,7 +14939,7 @@
         <v>2003</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75">
@@ -15037,7 +14953,7 @@
         <v>2004</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75">
@@ -15051,7 +14967,7 @@
         <v>2005</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75">
@@ -15065,7 +14981,7 @@
         <v>2006</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75">
@@ -15079,7 +14995,7 @@
         <v>2007</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75">
@@ -15093,7 +15009,7 @@
         <v>2008</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75">
@@ -15107,7 +15023,7 @@
         <v>2009</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75">
@@ -15121,7 +15037,7 @@
         <v>2010</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75">
@@ -15135,7 +15051,7 @@
         <v>2011</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75">
@@ -15149,7 +15065,7 @@
         <v>2012</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75">
@@ -15163,7 +15079,7 @@
         <v>2013</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75">
@@ -15177,7 +15093,7 @@
         <v>2014</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75">
@@ -15191,7 +15107,7 @@
         <v>2015</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75">
@@ -15205,7 +15121,7 @@
         <v>2016</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75">
@@ -15219,7 +15135,7 @@
         <v>2017</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75">
@@ -15233,7 +15149,7 @@
         <v>2018</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75">
@@ -15247,7 +15163,7 @@
         <v>2019</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75">
@@ -15261,7 +15177,7 @@
         <v>2020</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75">
@@ -15275,7 +15191,7 @@
         <v>2021</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75">
@@ -15289,7 +15205,7 @@
         <v>2022</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75">
@@ -15303,7 +15219,7 @@
         <v>2000</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75">
@@ -15317,7 +15233,7 @@
         <v>2001</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75">
@@ -15331,7 +15247,7 @@
         <v>2002</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75">
@@ -15345,7 +15261,7 @@
         <v>2003</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75">
@@ -15359,7 +15275,7 @@
         <v>2004</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75">
@@ -15373,7 +15289,7 @@
         <v>2005</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75">
@@ -15387,7 +15303,7 @@
         <v>2006</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75">
@@ -15401,7 +15317,7 @@
         <v>2007</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75">
@@ -15415,7 +15331,7 @@
         <v>2008</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75">
@@ -15429,7 +15345,7 @@
         <v>2009</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75">
@@ -15443,7 +15359,7 @@
         <v>2010</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75">
@@ -15457,7 +15373,7 @@
         <v>2011</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75">
@@ -15471,7 +15387,7 @@
         <v>2012</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75">
@@ -15485,7 +15401,7 @@
         <v>2013</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75">
@@ -15499,7 +15415,7 @@
         <v>2014</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75">
@@ -15513,7 +15429,7 @@
         <v>2015</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75">
@@ -15527,7 +15443,7 @@
         <v>2016</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75">
@@ -15541,7 +15457,7 @@
         <v>2017</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75">
@@ -15555,7 +15471,7 @@
         <v>2018</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75">
@@ -15569,7 +15485,7 @@
         <v>2019</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75">
@@ -15583,7 +15499,7 @@
         <v>2020</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75">
@@ -15597,7 +15513,7 @@
         <v>2021</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75">
@@ -15611,7 +15527,7 @@
         <v>2022</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75">
@@ -15625,7 +15541,7 @@
         <v>2000</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75">
@@ -15639,7 +15555,7 @@
         <v>2001</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75">
@@ -15653,7 +15569,7 @@
         <v>2002</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75">
@@ -15667,7 +15583,7 @@
         <v>2003</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75">
@@ -15681,7 +15597,7 @@
         <v>2004</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75">
@@ -15695,7 +15611,7 @@
         <v>2005</v>
       </c>
       <c r="D168" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75">
@@ -15709,7 +15625,7 @@
         <v>2006</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75">
@@ -15723,7 +15639,7 @@
         <v>2007</v>
       </c>
       <c r="D170" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75">
@@ -15737,7 +15653,7 @@
         <v>2008</v>
       </c>
       <c r="D171" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75">
@@ -15751,7 +15667,7 @@
         <v>2009</v>
       </c>
       <c r="D172" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75">
@@ -15765,7 +15681,7 @@
         <v>2010</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75">
@@ -15779,7 +15695,7 @@
         <v>2011</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75">
@@ -15793,7 +15709,7 @@
         <v>2012</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75">
@@ -15807,7 +15723,7 @@
         <v>2013</v>
       </c>
       <c r="D176" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75">
@@ -15821,7 +15737,7 @@
         <v>2014</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75">
@@ -15835,7 +15751,7 @@
         <v>2015</v>
       </c>
       <c r="D178" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75">
@@ -15849,7 +15765,7 @@
         <v>2016</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75">
@@ -15863,7 +15779,7 @@
         <v>2017</v>
       </c>
       <c r="D180" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75">
@@ -15877,7 +15793,7 @@
         <v>2018</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75">
@@ -15891,7 +15807,7 @@
         <v>2019</v>
       </c>
       <c r="D182" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75">
@@ -15905,7 +15821,7 @@
         <v>2020</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75">
@@ -15919,7 +15835,7 @@
         <v>2021</v>
       </c>
       <c r="D184" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75">
@@ -15933,7 +15849,7 @@
         <v>2022</v>
       </c>
       <c r="D185" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75">
@@ -15947,7 +15863,7 @@
         <v>2000</v>
       </c>
       <c r="D186" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75">
@@ -15961,7 +15877,7 @@
         <v>2001</v>
       </c>
       <c r="D187" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75">
@@ -15975,7 +15891,7 @@
         <v>2002</v>
       </c>
       <c r="D188" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75">
@@ -15989,7 +15905,7 @@
         <v>2003</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75">
@@ -16003,7 +15919,7 @@
         <v>2004</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75">
@@ -16017,7 +15933,7 @@
         <v>2005</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75">
@@ -16031,7 +15947,7 @@
         <v>2006</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75">
@@ -16045,7 +15961,7 @@
         <v>2007</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75">
@@ -16059,7 +15975,7 @@
         <v>2008</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75">
@@ -16073,7 +15989,7 @@
         <v>2009</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75">
@@ -16087,7 +16003,7 @@
         <v>2010</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75">
@@ -16101,7 +16017,7 @@
         <v>2011</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75">
@@ -16115,7 +16031,7 @@
         <v>2012</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75">
@@ -16129,7 +16045,7 @@
         <v>2013</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75">
@@ -16143,7 +16059,7 @@
         <v>2014</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75">
@@ -16157,7 +16073,7 @@
         <v>2015</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75">
@@ -16171,7 +16087,7 @@
         <v>2016</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75">
@@ -16185,7 +16101,7 @@
         <v>2017</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75">
@@ -16199,7 +16115,7 @@
         <v>2018</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75">
@@ -16213,7 +16129,7 @@
         <v>2019</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75">
@@ -16227,7 +16143,7 @@
         <v>2020</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75">
@@ -16241,7 +16157,7 @@
         <v>2021</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75">
@@ -16255,7 +16171,7 @@
         <v>2022</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75">
@@ -16269,7 +16185,7 @@
         <v>2000</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75">
@@ -16283,7 +16199,7 @@
         <v>2001</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75">
@@ -16297,7 +16213,7 @@
         <v>2002</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75">
@@ -16311,7 +16227,7 @@
         <v>2003</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75">
@@ -16325,7 +16241,7 @@
         <v>2004</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75">
@@ -16339,7 +16255,7 @@
         <v>2005</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75">
@@ -16353,7 +16269,7 @@
         <v>2006</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75">
@@ -16367,7 +16283,7 @@
         <v>2007</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75">
@@ -16381,7 +16297,7 @@
         <v>2008</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75">
@@ -16395,7 +16311,7 @@
         <v>2009</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75">
@@ -16409,7 +16325,7 @@
         <v>2010</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75">
@@ -16423,7 +16339,7 @@
         <v>2011</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75">
@@ -16437,7 +16353,7 @@
         <v>2012</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75">
@@ -16451,7 +16367,7 @@
         <v>2013</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75">
@@ -16465,7 +16381,7 @@
         <v>2014</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75">
@@ -16479,7 +16395,7 @@
         <v>2015</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75">
@@ -16493,7 +16409,7 @@
         <v>2016</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75">
@@ -16507,7 +16423,7 @@
         <v>2017</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75">
@@ -16521,7 +16437,7 @@
         <v>2018</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75">
@@ -16535,7 +16451,7 @@
         <v>2019</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75">
@@ -16549,7 +16465,7 @@
         <v>2020</v>
       </c>
       <c r="D229" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75">
@@ -16563,7 +16479,7 @@
         <v>2021</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75">
@@ -16577,7 +16493,7 @@
         <v>2022</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75">
@@ -16589,7 +16505,7 @@
         <v>2000</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75">
@@ -16601,7 +16517,7 @@
         <v>2001</v>
       </c>
       <c r="D233" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75">
@@ -16613,7 +16529,7 @@
         <v>2002</v>
       </c>
       <c r="D234" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75">
@@ -16627,7 +16543,7 @@
         <v>2003</v>
       </c>
       <c r="D235" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75">
@@ -16641,7 +16557,7 @@
         <v>2004</v>
       </c>
       <c r="D236" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75">
@@ -16655,7 +16571,7 @@
         <v>2005</v>
       </c>
       <c r="D237" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75">
@@ -16669,7 +16585,7 @@
         <v>2006</v>
       </c>
       <c r="D238" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75">
@@ -16683,7 +16599,7 @@
         <v>2007</v>
       </c>
       <c r="D239" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75">
@@ -16697,7 +16613,7 @@
         <v>2008</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75">
@@ -16711,7 +16627,7 @@
         <v>2009</v>
       </c>
       <c r="D241" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75">
@@ -16725,7 +16641,7 @@
         <v>2010</v>
       </c>
       <c r="D242" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75">
@@ -16739,7 +16655,7 @@
         <v>2011</v>
       </c>
       <c r="D243" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75">
@@ -16753,7 +16669,7 @@
         <v>2012</v>
       </c>
       <c r="D244" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75">
@@ -16767,7 +16683,7 @@
         <v>2013</v>
       </c>
       <c r="D245" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75">
@@ -16781,7 +16697,7 @@
         <v>2014</v>
       </c>
       <c r="D246" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75">
@@ -16795,7 +16711,7 @@
         <v>2015</v>
       </c>
       <c r="D247" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75">
@@ -16809,7 +16725,7 @@
         <v>2016</v>
       </c>
       <c r="D248" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75">
@@ -16823,7 +16739,7 @@
         <v>2017</v>
       </c>
       <c r="D249" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75">
@@ -16837,7 +16753,7 @@
         <v>2018</v>
       </c>
       <c r="D250" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75">
@@ -16851,7 +16767,7 @@
         <v>2019</v>
       </c>
       <c r="D251" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75">
@@ -16865,7 +16781,7 @@
         <v>2020</v>
       </c>
       <c r="D252" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75">
@@ -16879,7 +16795,7 @@
         <v>2021</v>
       </c>
       <c r="D253" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75">
@@ -16893,7 +16809,7 @@
         <v>2022</v>
       </c>
       <c r="D254" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75">
@@ -16907,7 +16823,7 @@
         <v>2000</v>
       </c>
       <c r="D255" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75">
@@ -16921,7 +16837,7 @@
         <v>2001</v>
       </c>
       <c r="D256" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75">
@@ -16935,7 +16851,7 @@
         <v>2002</v>
       </c>
       <c r="D257" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75">
@@ -16949,7 +16865,7 @@
         <v>2003</v>
       </c>
       <c r="D258" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75">
@@ -16963,7 +16879,7 @@
         <v>2004</v>
       </c>
       <c r="D259" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75">
@@ -16977,7 +16893,7 @@
         <v>2005</v>
       </c>
       <c r="D260" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75">
@@ -16991,7 +16907,7 @@
         <v>2006</v>
       </c>
       <c r="D261" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75">
@@ -17005,7 +16921,7 @@
         <v>2007</v>
       </c>
       <c r="D262" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75">
@@ -17019,7 +16935,7 @@
         <v>2008</v>
       </c>
       <c r="D263" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75">
@@ -17033,7 +16949,7 @@
         <v>2009</v>
       </c>
       <c r="D264" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75">
@@ -17047,7 +16963,7 @@
         <v>2010</v>
       </c>
       <c r="D265" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75">
@@ -17061,7 +16977,7 @@
         <v>2011</v>
       </c>
       <c r="D266" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75">
@@ -17075,7 +16991,7 @@
         <v>2012</v>
       </c>
       <c r="D267" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75">
@@ -17089,7 +17005,7 @@
         <v>2013</v>
       </c>
       <c r="D268" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75">
@@ -17103,7 +17019,7 @@
         <v>2014</v>
       </c>
       <c r="D269" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75">
@@ -17117,7 +17033,7 @@
         <v>2015</v>
       </c>
       <c r="D270" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75">
@@ -17131,7 +17047,7 @@
         <v>2016</v>
       </c>
       <c r="D271" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75">
@@ -17145,7 +17061,7 @@
         <v>2017</v>
       </c>
       <c r="D272" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75">
@@ -17159,7 +17075,7 @@
         <v>2018</v>
       </c>
       <c r="D273" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75">
@@ -17173,7 +17089,7 @@
         <v>2019</v>
       </c>
       <c r="D274" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75">
@@ -17187,7 +17103,7 @@
         <v>2020</v>
       </c>
       <c r="D275" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75">
@@ -17201,7 +17117,7 @@
         <v>2021</v>
       </c>
       <c r="D276" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75">
@@ -17215,7 +17131,7 @@
         <v>2022</v>
       </c>
       <c r="D277" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75">
@@ -17229,7 +17145,7 @@
         <v>2000</v>
       </c>
       <c r="D278" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75">
@@ -17243,7 +17159,7 @@
         <v>2001</v>
       </c>
       <c r="D279" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75">
@@ -17257,7 +17173,7 @@
         <v>2002</v>
       </c>
       <c r="D280" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75">
@@ -17271,7 +17187,7 @@
         <v>2003</v>
       </c>
       <c r="D281" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75">
@@ -17285,7 +17201,7 @@
         <v>2004</v>
       </c>
       <c r="D282" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75">
@@ -17299,7 +17215,7 @@
         <v>2005</v>
       </c>
       <c r="D283" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75">
@@ -17313,7 +17229,7 @@
         <v>2006</v>
       </c>
       <c r="D284" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75">
@@ -17327,7 +17243,7 @@
         <v>2007</v>
       </c>
       <c r="D285" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75">
@@ -17341,7 +17257,7 @@
         <v>2008</v>
       </c>
       <c r="D286" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75">
@@ -17355,7 +17271,7 @@
         <v>2009</v>
       </c>
       <c r="D287" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75">
@@ -17369,7 +17285,7 @@
         <v>2010</v>
       </c>
       <c r="D288" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75">
@@ -17383,7 +17299,7 @@
         <v>2011</v>
       </c>
       <c r="D289" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75">
@@ -17397,7 +17313,7 @@
         <v>2012</v>
       </c>
       <c r="D290" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75">
@@ -17411,7 +17327,7 @@
         <v>2013</v>
       </c>
       <c r="D291" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75">
@@ -17425,7 +17341,7 @@
         <v>2014</v>
       </c>
       <c r="D292" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75">
@@ -17439,7 +17355,7 @@
         <v>2015</v>
       </c>
       <c r="D293" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75">
@@ -17453,7 +17369,7 @@
         <v>2016</v>
       </c>
       <c r="D294" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75">
@@ -17467,7 +17383,7 @@
         <v>2017</v>
       </c>
       <c r="D295" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75">
@@ -17481,7 +17397,7 @@
         <v>2018</v>
       </c>
       <c r="D296" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75">
@@ -17495,7 +17411,7 @@
         <v>2019</v>
       </c>
       <c r="D297" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75">
@@ -17509,7 +17425,7 @@
         <v>2020</v>
       </c>
       <c r="D298" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75">
@@ -17523,7 +17439,7 @@
         <v>2021</v>
       </c>
       <c r="D299" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75">
@@ -17537,7 +17453,7 @@
         <v>2022</v>
       </c>
       <c r="D300" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -17555,7 +17471,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="B1">
         <v>2000</v>
@@ -17653,7 +17569,7 @@
     </row>
     <row r="2" spans="1:32">
       <c r="A2" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="B2" s="13">
         <v>18.399999999999999</v>
@@ -17751,7 +17667,7 @@
     </row>
     <row r="3" spans="1:32">
       <c r="A3" t="s">
-        <v>355</v>
+        <v>327</v>
       </c>
       <c r="B3" s="13">
         <v>0.2</v>
@@ -17849,7 +17765,7 @@
     </row>
     <row r="4" spans="1:32">
       <c r="A4" t="s">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="B4" s="13">
         <v>17</v>
@@ -18143,7 +18059,7 @@
     </row>
     <row r="7" spans="1:32">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="B7" s="13">
         <v>1.2</v>
@@ -19194,26 +19110,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -19454,8 +19350,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19463,5 +19379,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}"/>
 </file>